--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-30.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-30.xlsx
@@ -558,19 +558,15 @@
       <c r="K2" t="n">
         <v>1.42</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-30.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-30.xlsx
@@ -558,15 +558,19 @@
       <c r="K2" t="n">
         <v>1.42</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x2</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
